--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basbrut_a_2022.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_basbrut_a_2022.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:34</t>
+    <t xml:space="preserve">2026-09-24 01:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -640,7 +640,7 @@
         <v>0.2</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         <v>0.13</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         <v>0.14</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13">
@@ -679,10 +679,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14">
@@ -707,7 +707,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.07</v>
+        <v>0.27</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>332</v>
@@ -721,7 +721,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>332</v>
@@ -735,7 +735,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>332</v>
